--- a/bams-backend/app/ds/llm/utils/Credit Card Mapping.xlsx
+++ b/bams-backend/app/ds/llm/utils/Credit Card Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ujjwal/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\bank-account-monitoring\bams-backend\app\ds\llm\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCE8DC94-5939-8F4A-B788-6388E53C5066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD48241-2E4F-4ACB-8FAF-0C7D73091807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{7BA3553A-1F5E-C747-8E94-6904FD75D38C}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="9420" xr2:uid="{7BA3553A-1F5E-C747-8E94-6904FD75D38C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -534,9 +532,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -601,21 +606,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B6B82C4C-F832-4BC8-943E-A772B4B5ECDD}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -948,17 +956,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57634242-DFBB-0C4D-B9E7-67252E62083F}">
   <dimension ref="A1:F67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -978,11 +986,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -996,11 +1004,11 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1014,11 +1022,11 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1032,11 +1040,11 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1052,11 +1060,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1072,11 +1080,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1092,11 +1100,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1112,11 +1120,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1132,11 +1140,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1152,11 +1160,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1172,11 +1180,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1192,11 +1200,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1212,11 +1220,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1232,11 +1240,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1252,11 +1260,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1272,11 +1280,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1292,11 +1300,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1312,11 +1320,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1330,11 +1338,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1348,11 +1356,11 @@
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1366,11 +1374,11 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1384,11 +1392,11 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1402,11 +1410,11 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1420,11 +1428,11 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1438,11 +1446,11 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -1458,12 +1466,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>73</v>
+      <c r="B27" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>48</v>
@@ -1478,11 +1486,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -1498,11 +1506,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -1516,12 +1524,12 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
+      <c r="B30" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>81</v>
@@ -1534,11 +1542,11 @@
       </c>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1554,11 +1562,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -1572,11 +1580,11 @@
       </c>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -1592,11 +1600,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1612,11 +1620,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -1632,11 +1640,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -1652,11 +1660,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -1672,11 +1680,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -1692,11 +1700,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -1710,11 +1718,11 @@
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -1730,11 +1738,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -1750,11 +1758,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -1770,11 +1778,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -1790,11 +1798,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -1808,11 +1816,11 @@
       </c>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -1828,11 +1836,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -1846,11 +1854,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -1866,11 +1874,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -1886,11 +1894,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -1906,11 +1914,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -1926,11 +1934,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -1946,11 +1954,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -1966,11 +1974,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -1986,11 +1994,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -2006,11 +2014,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -2026,11 +2034,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -2046,12 +2054,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>143</v>
+      <c r="B57" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>146</v>
@@ -2066,11 +2074,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -2084,12 +2092,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>143</v>
+      <c r="B59" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>48</v>
@@ -2104,12 +2112,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>143</v>
+      <c r="B60" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>151</v>
@@ -2122,11 +2130,11 @@
       </c>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -2142,11 +2150,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -2162,11 +2170,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -2182,11 +2190,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -2202,12 +2210,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>83</v>
+      <c r="B65" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>157</v>
@@ -2222,11 +2230,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -2242,11 +2250,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C67" s="1" t="s">
